--- a/output/FINAL_REPORT.xlsx
+++ b/output/FINAL_REPORT.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>83 sec</t>
+          <t>99 sec</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9187,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DATE              : 05.08.2026</t>
+          <t>DATE              : 06.08.2026</t>
         </is>
       </c>
     </row>
